--- a/artfynd/A 1506-2024 artfynd.xlsx
+++ b/artfynd/A 1506-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129157124</v>
+        <v>129156598</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>349685</v>
+        <v>349747</v>
       </c>
       <c r="R2" t="n">
-        <v>6615430</v>
+        <v>6615431</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Elin Rostedt</t>
+          <t>Mikael Andersson</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson, Per Karlsson Linderum, Ellen Payne, Magnus Sjölund, Sofie von Knorring</t>
+          <t>Väg och Miljö AB, Per Karlsson Linderum, Elin Rostedt, Ellen Payne, Magnus Sjölund, Sofie von Knorring</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129156598</v>
+        <v>129157124</v>
       </c>
       <c r="B3" t="n">
-        <v>97525</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,34 +792,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krokebol, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>349747</v>
+        <v>349685</v>
       </c>
       <c r="R3" t="n">
-        <v>6615431</v>
+        <v>6615430</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +869,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Mikael Andersson</t>
+          <t>Elin Rostedt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -876,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Elin Rostedt, Ellen Payne, Magnus Sjölund, Sofie von Knorring</t>
+          <t>Väg och Miljö AB, Mikael Andersson, Per Karlsson Linderum, Ellen Payne, Magnus Sjölund, Sofie von Knorring</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 1506-2024 artfynd.xlsx
+++ b/artfynd/A 1506-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129156598</v>
+        <v>129169234</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -757,11 +757,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Mikael Andersson</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -770,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Per Karlsson Linderum, Elin Rostedt, Ellen Payne, Magnus Sjölund, Sofie von Knorring</t>
+          <t>Väg och Miljö AB, Elin Rostedt, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129157124</v>
+        <v>129169293</v>
       </c>
       <c r="B3" t="n">
         <v>5177</v>
@@ -810,15 +805,6 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krokebol, Vrm</t>
@@ -869,15 +855,9 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Elin Rostedt</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -886,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson, Per Karlsson Linderum, Ellen Payne, Magnus Sjölund, Sofie von Knorring</t>
+          <t>Väg och Miljö AB, Mikael Andersson, Elin Rostedt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 1506-2024 artfynd.xlsx
+++ b/artfynd/A 1506-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129169234</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1506-2024 artfynd.xlsx
+++ b/artfynd/A 1506-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129169234</v>
       </c>
       <c r="B2" t="n">
-        <v>97543</v>
+        <v>97550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1506-2024 artfynd.xlsx
+++ b/artfynd/A 1506-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129169234</v>
       </c>
       <c r="B2" t="n">
-        <v>97550</v>
+        <v>97552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1506-2024 artfynd.xlsx
+++ b/artfynd/A 1506-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129169234</v>
       </c>
       <c r="B2" t="n">
-        <v>97552</v>
+        <v>97578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1506-2024 artfynd.xlsx
+++ b/artfynd/A 1506-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129169234</v>
       </c>
       <c r="B2" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1506-2024 artfynd.xlsx
+++ b/artfynd/A 1506-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129169234</v>
       </c>
       <c r="B2" t="n">
-        <v>97579</v>
+        <v>97580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1506-2024 artfynd.xlsx
+++ b/artfynd/A 1506-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129169234</v>
       </c>
       <c r="B2" t="n">
-        <v>97580</v>
+        <v>97584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1506-2024 artfynd.xlsx
+++ b/artfynd/A 1506-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129169234</v>
+        <v>129169194</v>
       </c>
       <c r="B2" t="n">
-        <v>97630</v>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>349747</v>
+        <v>349655</v>
       </c>
       <c r="R2" t="n">
-        <v>6615431</v>
+        <v>6615444</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elin Rostedt, Mikael Andersson</t>
+          <t>Väg och Miljö AB, Mikael Andersson, Elin Rostedt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -779,7 +779,7 @@
         <v>129169293</v>
       </c>
       <c r="B3" t="n">
-        <v>5177</v>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -866,10 +866,208 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson, Elin Rostedt</t>
+          <t>Elin Rostedt, Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129169269</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Krokebol, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>349623</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6615361</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älgå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Rostedt, Mikael Andersson, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129169234</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Krokebol, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>349747</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6615431</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älgå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Elin Rostedt, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Naturvärdesinventering</t>
         </is>
